--- a/data/trans_camb/IP16_n_R2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16_n_R2-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-56,43; -12,73</t>
+          <t>-53,33; -12,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-49,11; -0,78</t>
+          <t>-48,15; -0,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,9; 32,02</t>
+          <t>-16,26; 31,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-37,74; 3,25</t>
+          <t>-36,15; 1,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-41,26; -2,98</t>
+          <t>-40,07; -1,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-23,56; 19,83</t>
+          <t>-20,16; 20,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-37,83; -10,16</t>
+          <t>-38,12; -8,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-38,21; -7,54</t>
+          <t>-37,19; -6,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,18; 16,68</t>
+          <t>-14,48; 19,26</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -31,31</t>
+          <t>-100,0; -29,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-94,86; 5,48</t>
+          <t>-91,88; 12,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-34,9; 134,63</t>
+          <t>-33,16; 125,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 39,7</t>
+          <t>-91,82; 32,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 14,84</t>
+          <t>-100,0; 17,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-59,37; 127,85</t>
+          <t>-57,55; 122,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-91,29; -31,81</t>
+          <t>-91,41; -36,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-91,27; -24,18</t>
+          <t>-89,52; -19,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-34,2; 72,18</t>
+          <t>-34,66; 82,84</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-39,79; 4,05</t>
+          <t>-41,04; 2,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-49,77; -10,29</t>
+          <t>-48,63; -9,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-32,17; 11,65</t>
+          <t>-36,13; 10,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-56,24; -11,51</t>
+          <t>-57,47; -13,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-49,54; -3,9</t>
+          <t>-49,22; -2,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-24,07; 28,59</t>
+          <t>-24,2; 26,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-41,88; -11,1</t>
+          <t>-41,23; -8,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-42,07; -11,77</t>
+          <t>-42,62; -11,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-22,88; 12,47</t>
+          <t>-22,6; 14,55</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-84,14; 28,01</t>
+          <t>-83,0; 22,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 10,88</t>
+          <t>-100,0; 7,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-70,6; 62,1</t>
+          <t>-74,61; 51,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 10,11</t>
+          <t>-100,0; -22,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-90,6; -7,2</t>
+          <t>-89,88; 11,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-42,31; 113,62</t>
+          <t>-45,27; 105,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-87,26; -28,67</t>
+          <t>-87,55; -27,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-90,03; -34,07</t>
+          <t>-91,28; -35,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-47,57; 42,97</t>
+          <t>-46,8; 54,35</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-39,78; 26,33</t>
+          <t>-34,74; 28,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-29,99; 35,44</t>
+          <t>-29,82; 34,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-41,08; 21,68</t>
+          <t>-40,63; 21,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-57,69; -6,21</t>
+          <t>-54,97; -1,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-70,51; -37,79</t>
+          <t>-70,04; -35,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-42,95; 10,45</t>
+          <t>-41,75; 10,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-40,15; -0,05</t>
+          <t>-41,29; -1,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-48,79; -11,14</t>
+          <t>-49,11; -10,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-36,17; 4,88</t>
+          <t>-35,56; 5,8</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1215,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-78,6; 158,3</t>
+          <t>-72,39; 202,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-68,76; 216,81</t>
+          <t>-62,64; 208,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-85,78; 158,72</t>
+          <t>-84,72; 151,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-91,0; -9,92</t>
+          <t>-87,95; -0,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-67,75; 26,21</t>
+          <t>-67,29; 22,71</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-73,88; 0,12</t>
+          <t>-74,5; -0,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-88,59; -26,4</t>
+          <t>-88,69; -26,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-63,28; 12,79</t>
+          <t>-62,86; 14,55</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-37,31; -4,31</t>
+          <t>-37,17; -6,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-42,73; -12,72</t>
+          <t>-41,88; -13,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-43,04; -2,52</t>
+          <t>-43,56; -4,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-43,15; -14,2</t>
+          <t>-43,02; -14,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-44,83; -14,98</t>
+          <t>-46,45; -15,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-20,69; 13,7</t>
+          <t>-20,89; 13,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-36,84; -16,1</t>
+          <t>-36,67; -15,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-39,4; -17,58</t>
+          <t>-39,86; -18,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-29,78; -1,02</t>
+          <t>-31,96; -0,66</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-77,66; -15,65</t>
+          <t>-75,27; -19,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-87,06; -38,22</t>
+          <t>-86,93; -43,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-83,99; -6,41</t>
+          <t>-83,57; -9,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-87,52; -42,25</t>
+          <t>-87,62; -44,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-91,8; -42,65</t>
+          <t>-91,67; -41,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-43,41; 45,9</t>
+          <t>-43,44; 45,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-77,81; -44,82</t>
+          <t>-78,41; -45,1</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-85,73; -55,14</t>
+          <t>-86,22; -55,76</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-65,33; -4,45</t>
+          <t>-69,81; -3,62</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-44,78; 0,65</t>
+          <t>-46,51; -2,54</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-53,46; -11,95</t>
+          <t>-52,98; -13,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-25,25; 23,21</t>
+          <t>-25,35; 21,23</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-27,21; 12,09</t>
+          <t>-25,85; 11,26</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-24,66; 14,73</t>
+          <t>-24,11; 16,73</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-18,32; 17,92</t>
+          <t>-20,13; 18,99</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-28,47; -0,21</t>
+          <t>-29,63; -0,31</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-32,18; -4,93</t>
+          <t>-32,97; -5,52</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-16,23; 14,89</t>
+          <t>-15,68; 13,94</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-82,73; 7,03</t>
+          <t>-83,37; -2,38</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-93,94; -33,53</t>
+          <t>-93,97; -32,15</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-46,95; 83,98</t>
+          <t>-45,51; 83,81</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-71,43; 94,45</t>
+          <t>-69,83; 74,92</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-65,19; 103,93</t>
+          <t>-67,22; 116,35</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-49,15; 113,32</t>
+          <t>-51,13; 111,92</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-67,51; 0,78</t>
+          <t>-69,33; 0,03</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-75,27; -15,07</t>
+          <t>-76,63; -18,31</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-37,93; 58,77</t>
+          <t>-36,12; 56,9</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-65,91; 11,8</t>
+          <t>-71,34; 4,92</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-75,98; -13,07</t>
+          <t>-75,91; -13,14</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-52,01; 20,42</t>
+          <t>-49,0; 21,75</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-57,95; 2,06</t>
+          <t>-59,97; -1,13</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-62,78; 2,15</t>
+          <t>-63,04; 4,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-47,73; 20,53</t>
+          <t>-44,92; 21,55</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-54,26; -6,54</t>
+          <t>-53,56; -5,26</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-59,62; -14,81</t>
+          <t>-59,63; -16,04</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-37,47; 11,05</t>
+          <t>-36,22; 12,9</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 75,39</t>
+          <t>-100,0; 33,56</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -14,9</t>
+          <t>-100,0; -11,41</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-67,69; 69,68</t>
+          <t>-66,99; 78,84</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-84,25; 10,62</t>
+          <t>-88,49; 2,2</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-90,92; 14,67</t>
+          <t>-89,96; 21,56</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-69,51; 51,65</t>
+          <t>-66,03; 59,81</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-82,94; -16,73</t>
+          <t>-81,89; -12,06</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-90,7; -37,27</t>
+          <t>-90,63; -37,07</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-55,93; 28,33</t>
+          <t>-55,57; 33,47</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-32,19; -12,84</t>
+          <t>-31,4; -12,41</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-37,29; -19,2</t>
+          <t>-35,8; -18,84</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-25,79; -0,09</t>
+          <t>-25,74; 0,43</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-33,83; -17,15</t>
+          <t>-33,9; -17,2</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-35,16; -18,22</t>
+          <t>-34,6; -19,01</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-14,29; 4,5</t>
+          <t>-15,48; 3,54</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-29,76; -18,02</t>
+          <t>-29,29; -17,27</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-33,15; -20,84</t>
+          <t>-33,18; -20,71</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-16,85; -1,06</t>
+          <t>-17,0; -1,0</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-70,4; -37,55</t>
+          <t>-69,47; -36,19</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-80,28; -53,57</t>
+          <t>-80,66; -53,58</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-55,31; -1,69</t>
+          <t>-58,23; 0,41</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-76,95; -49,36</t>
+          <t>-76,47; -46,93</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-78,48; -50,43</t>
+          <t>-79,42; -51,59</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-32,24; 12,87</t>
+          <t>-34,33; 11,21</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-68,8; -48,48</t>
+          <t>-68,45; -47,51</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-76,8; -57,8</t>
+          <t>-76,67; -57,52</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-40,07; -3,09</t>
+          <t>-40,25; -3,43</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16_n_R2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16_n_R2-Clase-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumen más de dos medicamentos</t>
+          <t>Menores que consumieron más de dos medicamentos en las últimas 2 semanas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-17,27</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-21,18</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-2,34</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-32,27</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-25,86</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6,86</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-17,27</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-21,18</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,74</t>
+          <t>7,81</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,36</t>
+          <t>2,84</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-53,33; -12,45</t>
+          <t>-35,56; 2,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-48,15; -0,82</t>
+          <t>-40,26; -3,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,26; 31,0</t>
+          <t>-25,02; 18,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-36,15; 1,56</t>
+          <t>-53,97; -10,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-40,07; -1,11</t>
+          <t>-46,42; 1,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,16; 20,18</t>
+          <t>-17,61; 31,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-38,12; -8,72</t>
+          <t>-37,9; -7,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-37,19; -6,41</t>
+          <t>-37,39; -6,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,48; 19,26</t>
+          <t>-14,47; 19,73</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-60,77%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-74,54%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-8,23%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-82,15%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-65,83%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>17,46%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-60,77%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-74,54%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-6,12%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -29,31</t>
+          <t>-90,99; 58,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-91,88; 12,01</t>
+          <t>-100,0; 26,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-33,16; 125,04</t>
+          <t>-65,29; 106,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-91,82; 32,79</t>
+          <t>-100,0; -14,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 17,29</t>
+          <t>-92,21; 37,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-57,55; 122,48</t>
+          <t>-32,94; 137,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-91,41; -36,04</t>
+          <t>-90,27; -22,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-89,52; -19,18</t>
+          <t>-89,83; -20,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-34,66; 82,84</t>
+          <t>-34,94; 83,4</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-36,58</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-27,67</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,69</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-18,3</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-29,86</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-10,77</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-36,58</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-27,67</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>-10,66</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-4,93</t>
+          <t>-4,41</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-41,04; 2,51</t>
+          <t>-56,0; -11,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-48,63; -9,09</t>
+          <t>-46,77; -1,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-36,13; 10,12</t>
+          <t>-23,7; 29,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-57,47; -13,91</t>
+          <t>-41,16; 2,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-49,22; -2,51</t>
+          <t>-51,61; -10,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-24,2; 26,94</t>
+          <t>-32,6; 11,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-41,23; -8,81</t>
+          <t>-41,42; -9,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-42,62; -11,77</t>
+          <t>-41,37; -11,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-22,6; 14,55</t>
+          <t>-21,13; 14,67</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-86,85%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-65,7%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-52,32%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-85,38%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-30,79%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-86,85%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-65,7%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>-30,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-12,83%</t>
+          <t>-11,49%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-83,0; 22,7</t>
+          <t>-100,0; -10,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 7,96</t>
+          <t>-91,77; -4,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-74,61; 51,24</t>
+          <t>-45,25; 123,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -22,45</t>
+          <t>-84,02; 25,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-89,88; 11,44</t>
+          <t>-100,0; 30,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-45,27; 105,77</t>
+          <t>-71,09; 52,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-87,55; -27,24</t>
+          <t>-86,72; -28,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-91,28; -35,65</t>
+          <t>-90,5; -34,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-46,8; 54,35</t>
+          <t>-45,13; 53,81</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-33,06</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-54,57</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-15,36</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-4,06</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,62</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-10,02</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-33,06</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-54,57</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-18,12</t>
+          <t>-10,11</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-15,66</t>
+          <t>-14,4</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-34,74; 28,76</t>
+          <t>-56,08; -1,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-29,82; 34,43</t>
+          <t>-70,72; -37,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-40,63; 21,64</t>
+          <t>-41,16; 11,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-54,97; -1,82</t>
+          <t>-33,72; 27,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-70,04; -35,16</t>
+          <t>-31,08; 33,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-41,75; 10,35</t>
+          <t>-38,44; 26,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-41,29; -1,53</t>
+          <t>-41,36; -0,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-49,11; -10,18</t>
+          <t>-48,53; -12,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-35,56; 5,8</t>
+          <t>-34,24; 5,85</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-60,58%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-28,14%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-12,0%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1,82%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-29,63%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-60,58%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-33,21%</t>
+          <t>-29,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-32,91%</t>
+          <t>-30,25%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-72,39; 202,57</t>
+          <t>-89,54; 3,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-62,64; 208,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-84,72; 151,38</t>
+          <t>-65,33; 29,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-87,95; -0,67</t>
+          <t>-73,04; 174,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-72,63; 219,64</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-67,29; 22,71</t>
+          <t>-81,14; 204,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-74,5; -0,11</t>
+          <t>-72,96; 0,5</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-88,69; -26,04</t>
+          <t>-88,03; -29,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-62,86; 14,55</t>
+          <t>-62,03; 15,52</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-29,07</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-30,83</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-4,6</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-21,76</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-28,8</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-21,02</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-29,07</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-30,83</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-3,75</t>
+          <t>-7,12</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-13,74</t>
+          <t>-5,76</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-37,17; -6,59</t>
+          <t>-43,41; -15,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-41,88; -13,63</t>
+          <t>-45,45; -16,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-43,56; -4,46</t>
+          <t>-22,87; 12,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-43,02; -14,77</t>
+          <t>-37,68; -6,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-46,45; -15,69</t>
+          <t>-42,58; -14,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-20,89; 13,1</t>
+          <t>-26,67; 10,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-36,67; -15,57</t>
+          <t>-36,6; -14,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-39,86; -18,31</t>
+          <t>-40,54; -19,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-31,96; -0,66</t>
+          <t>-17,84; 7,18</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-72,48%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-76,88%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-11,48%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-54,4%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-72,0%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-52,56%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-72,48%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-76,88%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-9,36%</t>
+          <t>-17,81%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-34,3%</t>
+          <t>-14,39%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-75,27; -19,74</t>
+          <t>-87,54; -44,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-86,93; -43,29</t>
+          <t>-92,55; -45,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-83,57; -9,09</t>
+          <t>-47,22; 40,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-87,62; -44,07</t>
+          <t>-77,36; -19,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-91,67; -41,24</t>
+          <t>-87,37; -45,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-43,44; 45,06</t>
+          <t>-55,07; 38,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-78,41; -45,1</t>
+          <t>-79,4; -43,12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-86,22; -55,76</t>
+          <t>-85,62; -55,81</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-69,81; -3,62</t>
+          <t>-38,24; 21,45</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-8,07</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-5,61</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0,61</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-23,11</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-32,57</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-1,13</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-8,07</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-5,61</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,22</t>
+          <t>-2,51</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,56</t>
+          <t>-0,44</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-46,51; -2,54</t>
+          <t>-29,39; 9,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-52,98; -13,02</t>
+          <t>-26,02; 16,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-25,35; 21,23</t>
+          <t>-21,06; 19,73</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-25,85; 11,26</t>
+          <t>-45,74; -1,51</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-24,11; 16,73</t>
+          <t>-51,14; -10,83</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-20,13; 18,99</t>
+          <t>-26,42; 20,7</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-29,63; -0,31</t>
+          <t>-29,1; -1,07</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-32,97; -5,52</t>
+          <t>-33,08; -4,13</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-15,68; 13,94</t>
+          <t>-15,48; 14,05</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-28,84%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-20,07%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-55,28%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-77,93%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-2,7%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-28,84%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-20,07%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-0,77%</t>
+          <t>-5,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-1,64%</t>
+          <t>-1,31%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-83,37; -2,38</t>
+          <t>-76,35; 67,74</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-93,97; -32,15</t>
+          <t>-67,98; 119,99</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-45,51; 83,81</t>
+          <t>-53,96; 119,22</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-69,83; 74,92</t>
+          <t>-84,17; -2,72</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-67,22; 116,35</t>
+          <t>-94,88; -40,42</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-51,13; 111,92</t>
+          <t>-46,53; 81,1</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-69,33; 0,03</t>
+          <t>-69,59; -2,62</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-76,63; -18,31</t>
+          <t>-75,49; -12,94</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-36,12; 56,9</t>
+          <t>-37,24; 54,6</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-30,62</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-33,27</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-13,55</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-35,07</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-45,49</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-15,44</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-30,62</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-33,27</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-13,92</t>
+          <t>-16,49</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-14,51</t>
+          <t>-14,8</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-71,34; 4,92</t>
+          <t>-57,43; 3,99</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-75,91; -13,14</t>
+          <t>-62,56; 2,6</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-49,0; 21,75</t>
+          <t>-48,26; 21,7</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-59,97; -1,13</t>
+          <t>-71,0; 9,56</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-63,04; 4,0</t>
+          <t>-74,41; -8,28</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-44,92; 21,55</t>
+          <t>-54,95; 19,21</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-53,56; -5,26</t>
+          <t>-54,78; -7,11</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-59,63; -16,04</t>
+          <t>-60,88; -16,71</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-36,22; 12,9</t>
+          <t>-37,6; 11,2</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-56,21%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-61,07%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-24,87%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-62,32%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-80,81%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-27,43%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-56,21%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-61,07%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-25,55%</t>
+          <t>-29,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-26,29%</t>
+          <t>-26,81%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 33,56</t>
+          <t>-83,96; 13,83</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -11,41</t>
+          <t>-91,67; 16,21</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-66,99; 78,84</t>
+          <t>-67,63; 60,49</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-88,49; 2,2</t>
+          <t>-100,0; 35,94</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-89,96; 21,56</t>
+          <t>-100,0; -16,7</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-66,03; 59,81</t>
+          <t>-72,17; 64,82</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-81,89; -12,06</t>
+          <t>-83,22; -17,08</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-90,63; -37,07</t>
+          <t>-90,4; -35,72</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-55,57; 33,47</t>
+          <t>-57,99; 27,04</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-25,55</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-27,06</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-5,5</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-22,31</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-27,71</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-10,92</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-25,55</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-27,06</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-5,79</t>
+          <t>-4,54</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-8,33</t>
+          <t>-5,05</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-31,4; -12,41</t>
+          <t>-33,61; -16,72</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-35,8; -18,84</t>
+          <t>-34,87; -17,9</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-25,74; 0,43</t>
+          <t>-14,33; 4,61</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-33,9; -17,2</t>
+          <t>-30,96; -12,75</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-34,6; -19,01</t>
+          <t>-36,89; -18,83</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-15,48; 3,54</t>
+          <t>-14,76; 5,47</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-29,29; -17,27</t>
+          <t>-29,88; -17,56</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-33,18; -20,71</t>
+          <t>-33,31; -20,88</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-17,0; -1,0</t>
+          <t>-11,64; 1,8</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-63,99%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-67,79%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-13,76%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-56,06%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-69,61%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-27,43%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-63,99%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-67,79%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-14,51%</t>
+          <t>-11,41%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-20,9%</t>
+          <t>-12,68%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-69,47; -36,19</t>
+          <t>-75,28; -47,78</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-80,66; -53,58</t>
+          <t>-78,92; -49,8</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-58,23; 0,41</t>
+          <t>-32,93; 12,75</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-76,47; -46,93</t>
+          <t>-68,84; -36,8</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-79,42; -51,59</t>
+          <t>-80,37; -53,5</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-34,33; 11,21</t>
+          <t>-33,16; 14,77</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-68,45; -47,51</t>
+          <t>-69,12; -48,13</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-76,67; -57,52</t>
+          <t>-77,19; -56,43</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-40,25; -3,43</t>
+          <t>-27,33; 5,24</t>
         </is>
       </c>
     </row>
